--- a/OfficeIMO.TestAssets/Documents/ExcelPivotCorpus/AllErrorRanking/bottom-count.xlsx
+++ b/OfficeIMO.TestAssets/Documents/ExcelPivotCorpus/AllErrorRanking/bottom-count.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\przemyslaw.klys.EVOTEC\.codex\worktrees\excel-csv-quality\OfficeIMO\OfficeIMO.TestAssets\Documents\ExcelPivotCorpus\AllErrorRanking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E92F043A-E230-41CD-A9CC-A0A84EE6F303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2077E568-2523-4729-AC24-41D7046CC05D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="16170" windowWidth="28996" windowHeight="15675" xr2:uid="{37A5E84E-7F75-4774-9607-1C191D877743}"/>
+    <workbookView xWindow="-98" yWindow="16170" windowWidth="28996" windowHeight="15675" xr2:uid="{E46D5475-1275-4674-B366-B38C55A72BFD}"/>
   </bookViews>
   <sheets>
     <sheet name="Grouped" sheetId="2" r:id="rId1"/>
@@ -122,7 +122,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46293.576841203707" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="3" xr:uid="{D546425A-91C6-45C6-8E7A-9623F628CF24}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46293.579407060184" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="3" xr:uid="{CD478149-1597-4ED8-AEBB-A22F223213A6}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:B4" sheet="Source"/>
   </cacheSource>
@@ -164,7 +164,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B92F382C-6CA4-4B57-893F-52F490CB449B}" name="AllErrorPivot" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F88B7564-67EF-4439-8CC7-DA8EDE2A0EA4}" name="AllErrorPivot" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A4:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="2">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" measureFilter="1">
@@ -531,7 +531,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{418DE7E2-3BD9-41AF-BAA6-CA60C75CDCF3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873A285A-2A22-47AE-83CD-08A2A429383B}">
   <dimension ref="A4:B6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -569,7 +569,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{452CBA95-633C-4E97-A22C-39FD4B6BB79D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A35EB842-91EC-4693-9001-3EE01459DE21}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
